--- a/config/excel/CfgCombatBuffs.xlsx
+++ b/config/excel/CfgCombatBuffs.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatBuffs" sheetId="1" r:id="R40d1b1459b4549a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatBuffs" sheetId="1" r:id="Rd3d96ad97db34ec2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="General"/>
+    <x:numFmt numFmtId="201" formatCode="@"/>
+  </x:numFmts>
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,8 +32,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +58,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -58,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -82,6 +111,27 @@
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -297,172 +347,201 @@
     <x:col min="11" max="11" width="18.700000762939453" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="9" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>DurationTicks</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>IntervalTicks</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>MaxStacks</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>Merge</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>MoveSpeedAddPerStack</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>AttackRangeAddPerStack</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>PeriodicDamagePerStack</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>OnApplyEffectIDs</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>OnTickEffectIDs</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>OnExpireEffectIDs</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="10" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="str">
+      <x:c r="I2" s="10" t="str">
         <x:v>int[]</x:v>
       </x:c>
-      <x:c r="J2" s="6" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>int[]</x:v>
       </x:c>
-      <x:c r="K2" s="6" t="str">
+      <x:c r="K2" s="10" t="str">
         <x:v>int[]</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="11" t="str">
         <x:v># Buff编号。</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="11" t="str">
         <x:v>Buff持续逻辑帧。</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="11" t="str">
         <x:v>周期效果间隔逻辑帧。</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="11" t="str">
         <x:v>最多层数。</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="11" t="str">
         <x:v>CombatBuffMerge枚举值。</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>每层移动速度增加值。</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
+      <x:c r="G3" s="11" t="str">
         <x:v>每层攻击范围增加值。</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="11" t="str">
         <x:v>每层周期伤害。</x:v>
       </x:c>
-      <x:c r="I3" s="8" t="str">
+      <x:c r="I3" s="11" t="str">
         <x:v>应用时顺序执行的效果。</x:v>
       </x:c>
-      <x:c r="J3" s="8" t="str">
+      <x:c r="J3" s="11" t="str">
         <x:v>周期时顺序执行的效果。</x:v>
       </x:c>
-      <x:c r="K3" s="8" t="str">
+      <x:c r="K3" s="11" t="str">
         <x:v>到期时顺序执行的效果。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
+      <x:c r="A4" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="n">
+      <x:c r="B4" s="12" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="n">
+      <x:c r="C4" s="12" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
+      <x:c r="D4" s="12" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" s="3" t="str"/>
-      <x:c r="J4" s="3" t="str">
+      <x:c r="E4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str"/>
+      <x:c r="J4" s="16" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="str"/>
+      <x:c r="K4" s="16" t="str"/>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="3" t="n">
+      <x:c r="A5" s="12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="n">
+      <x:c r="B5" s="12" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="n">
+      <x:c r="C5" s="12" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
+      <x:c r="D5" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="n">
+      <x:c r="E5" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="3" t="str">
+      <x:c r="G5" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="16" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="str"/>
-      <x:c r="K5" s="3" t="str"/>
+      <x:c r="J5" s="16" t="str"/>
+      <x:c r="K5" s="16" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str"/>
+      <x:c r="J6" s="17" t="str"/>
+      <x:c r="K6" s="17" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
